--- a/exports/BAJAJFINSV_full_report.xlsx
+++ b/exports/BAJAJFINSV_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.75</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1805.45</v>
+        <v>1751.4</v>
       </c>
       <c r="I2" t="n">
         <v>1756.998812524412</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>1.12</v>
+        <v>-1.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.98</v>
       </c>
       <c r="M2" t="n">
         <v>0.79</v>
       </c>
       <c r="N2" t="n">
-        <v>1.06</v>
+        <v>4.46</v>
       </c>
       <c r="O2" t="n">
         <v>0.32</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>1592.4</v>
+        <v>1669.85</v>
       </c>
       <c r="I3" t="n">
         <v>1645.066056700724</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>9.08</v>
+        <v>4.66</v>
       </c>
       <c r="L3" t="n">
         <v>4.27</v>
@@ -612,7 +647,7 @@
         <v>2.63</v>
       </c>
       <c r="N3" t="n">
-        <v>3.36</v>
+        <v>4.85</v>
       </c>
       <c r="O3" t="n">
         <v>-4.46</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>10.33</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44616.38541666666</v>
+        <v>44616.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1554</v>
+        <v>1525</v>
       </c>
       <c r="I4" t="n">
         <v>1542.765500201054</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.94</v>
+        <v>-8.67</v>
       </c>
       <c r="L4" t="n">
-        <v>8.380000000000001</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M4" t="n">
         <v>4.3</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>8.09</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1502.8</v>
+        <v>1569.8</v>
       </c>
       <c r="I5" t="n">
         <v>1555.650635573191</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1.46</v>
+        <v>-2.94</v>
       </c>
       <c r="L5" t="n">
         <v>7.2</v>
       </c>
       <c r="M5" t="n">
-        <v>3.53</v>
+        <v>4.13</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.59</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1657</v>
+        <v>1626</v>
       </c>
       <c r="I6" t="n">
         <v>1636.644374275508</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>5.55</v>
+        <v>3.58</v>
       </c>
       <c r="L6" t="n">
         <v>2.66</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>5.16</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1139.5</v>
+        <v>1169.2</v>
       </c>
       <c r="I7" t="n">
         <v>1163.793975112832</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
-        <v>29.92</v>
+        <v>28.09</v>
       </c>
       <c r="L7" t="n">
         <v>1.49</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>6.99</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44795.38541666666</v>
+        <v>44795.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1600.4</v>
+        <v>1588.5</v>
       </c>
       <c r="I8" t="n">
         <v>1600.130710342921</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>36.88</v>
+        <v>35.86</v>
       </c>
       <c r="L8" t="n">
         <v>2.41</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>6.29</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1615</v>
+        <v>1689</v>
       </c>
       <c r="I9" t="n">
         <v>1688.464997989648</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.67</v>
+        <v>-6.33</v>
       </c>
       <c r="L9" t="n">
-        <v>4.47</v>
+        <v>6.69</v>
       </c>
       <c r="M9" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="N9" t="n">
-        <v>2.93</v>
+        <v>5.09</v>
       </c>
       <c r="O9" t="n">
         <v>-2.46</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.45</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44830.38541666666</v>
+        <v>44830.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>1729.25</v>
+        <v>1677.8</v>
       </c>
       <c r="I10" t="n">
         <v>1708.533983672969</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>2.38</v>
+        <v>-0.66</v>
       </c>
       <c r="L10" t="n">
         <v>2.96</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.81</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44867.55208333334</v>
+        <v>44868.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1710.95</v>
+        <v>1723.95</v>
       </c>
       <c r="I11" t="n">
         <v>1718.953802562335</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>37</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.98</v>
+        <v>-2.75</v>
       </c>
       <c r="L11" t="n">
         <v>3.72</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>5.02</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>1755.8</v>
+        <v>1698.25</v>
       </c>
       <c r="I12" t="n">
         <v>1707.559340533594</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>1.85</v>
+        <v>-1.49</v>
       </c>
       <c r="L12" t="n">
         <v>1.68</v>
@@ -1125,7 +1268,7 @@
         <v>0.76</v>
       </c>
       <c r="N12" t="n">
-        <v>1.35</v>
+        <v>2.89</v>
       </c>
       <c r="O12" t="n">
         <v>0.72</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.32</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1349</v>
+        <v>1370.5</v>
       </c>
       <c r="I13" t="n">
         <v>1355.024500146793</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>89.16666666666667</v>
+        <v>90</v>
       </c>
       <c r="K13" t="n">
-        <v>20.57</v>
+        <v>19.3</v>
       </c>
       <c r="L13" t="n">
         <v>3.45</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>6.73</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44979.38541666666</v>
+        <v>44979.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>1363.2</v>
+        <v>1360</v>
       </c>
       <c r="I14" t="n">
         <v>1360.658462251375</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.53</v>
+        <v>-0.77</v>
       </c>
       <c r="L14" t="n">
         <v>1.85</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>4.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45021.55208333334</v>
+        <v>45022.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1278</v>
+        <v>1306.6</v>
       </c>
       <c r="I15" t="n">
         <v>1297.354784741241</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>42</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K15" t="n">
-        <v>6.03</v>
+        <v>3.93</v>
       </c>
       <c r="L15" t="n">
         <v>2.9</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.57</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1616</v>
+        <v>1587</v>
       </c>
       <c r="I16" t="n">
         <v>1591.626903893874</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>112.1666666666667</v>
+        <v>113</v>
       </c>
       <c r="K16" t="n">
-        <v>23.68</v>
+        <v>21.46</v>
       </c>
       <c r="L16" t="n">
         <v>2.64</v>
@@ -1353,7 +1544,7 @@
         <v>0.43</v>
       </c>
       <c r="N16" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="O16" t="n">
         <v>2.15</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>154</v>
+        <v>155</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.3</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>1506.6</v>
+        <v>1519</v>
       </c>
       <c r="I17" t="n">
         <v>1516.865657192465</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>5.07</v>
+        <v>4.28</v>
       </c>
       <c r="L17" t="n">
         <v>2.71</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>3.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45224.55208333334</v>
+        <v>45225.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1605.9</v>
+        <v>1574.2</v>
       </c>
       <c r="I18" t="n">
         <v>1600.438105706954</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>49</v>
+        <v>49.83333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>5.72</v>
+        <v>3.63</v>
       </c>
       <c r="L18" t="n">
         <v>0.97</v>
@@ -1467,7 +1682,7 @@
         <v>1.64</v>
       </c>
       <c r="N18" t="n">
-        <v>1.99</v>
+        <v>3.05</v>
       </c>
       <c r="O18" t="n">
         <v>0.53</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.34</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45252.55208333334</v>
+        <v>45253.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1622</v>
+        <v>1628.05</v>
       </c>
       <c r="I19" t="n">
         <v>1626.451381111805</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.04</v>
+        <v>-3.42</v>
       </c>
       <c r="L19" t="n">
-        <v>3.42</v>
+        <v>3.98</v>
       </c>
       <c r="M19" t="n">
         <v>2.56</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>3.87</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1675</v>
+        <v>1655.75</v>
       </c>
       <c r="I20" t="n">
         <v>1670.790370227065</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K20" t="n">
-        <v>2.88</v>
+        <v>1.7</v>
       </c>
       <c r="L20" t="n">
         <v>0.99</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>4.8</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>1625</v>
+        <v>1651.05</v>
       </c>
       <c r="I21" t="n">
         <v>1647.159382694898</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K21" t="n">
-        <v>1.86</v>
+        <v>0.28</v>
       </c>
       <c r="L21" t="n">
         <v>4.12</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>4.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45329.55208333334</v>
+        <v>45330.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1594.85</v>
+        <v>1577.5</v>
       </c>
       <c r="I22" t="n">
         <v>1583.42395020599</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K22" t="n">
-        <v>-3.4</v>
+        <v>-4.45</v>
       </c>
       <c r="L22" t="n">
-        <v>4.39</v>
+        <v>4.85</v>
       </c>
       <c r="M22" t="n">
         <v>0.3</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>1585</v>
+        <v>1648.55</v>
       </c>
       <c r="I23" t="n">
         <v>1626.338372255469</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.48</v>
+        <v>-4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="M23" t="n">
         <v>0.83</v>
       </c>
       <c r="N23" t="n">
-        <v>2.77</v>
+        <v>3.91</v>
       </c>
       <c r="O23" t="n">
         <v>-1.12</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.49</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1661</v>
+        <v>1619.1</v>
       </c>
       <c r="I24" t="n">
         <v>1645.645989717288</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K24" t="n">
-        <v>0.76</v>
+        <v>-1.79</v>
       </c>
       <c r="L24" t="n">
         <v>3.67</v>
       </c>
       <c r="M24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="N24" t="n">
-        <v>1.89</v>
+        <v>2.57</v>
       </c>
       <c r="O24" t="n">
         <v>3.91</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>4.99</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45407.38541666666</v>
+        <v>45407.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>1644.3</v>
+        <v>1654</v>
       </c>
       <c r="I25" t="n">
         <v>1651.91584750836</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.56</v>
+        <v>-2.16</v>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>3.27</v>
       </c>
       <c r="M25" t="n">
         <v>0.52</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>4.29</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1601.55</v>
+        <v>1569</v>
       </c>
       <c r="I26" t="n">
         <v>1583.051869247362</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.17</v>
+        <v>-5.14</v>
       </c>
       <c r="L26" t="n">
-        <v>4.57</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
         <v>0.71</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.6</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45461.38541666666</v>
+        <v>45461.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>1587</v>
+        <v>1597.35</v>
       </c>
       <c r="I27" t="n">
         <v>1591.883675144968</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.15</v>
+        <v>-1.81</v>
       </c>
       <c r="L27" t="n">
         <v>3.25</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.27</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45496.55208333334</v>
+        <v>45497.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1610</v>
+        <v>1570.5</v>
       </c>
       <c r="I28" t="n">
         <v>1596.361996142683</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35</v>
+        <v>35.83333333333334</v>
       </c>
       <c r="K28" t="n">
-        <v>0.79</v>
+        <v>-1.68</v>
       </c>
       <c r="L28" t="n">
         <v>2.28</v>
@@ -2037,7 +2372,7 @@
         <v>0.62</v>
       </c>
       <c r="N28" t="n">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="O28" t="n">
         <v>0.65</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.96</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>1618</v>
+        <v>1658.95</v>
       </c>
       <c r="I29" t="n">
         <v>1643.013585707772</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.02</v>
+        <v>-5.63</v>
       </c>
       <c r="L29" t="n">
-        <v>3.47</v>
+        <v>5.76</v>
       </c>
       <c r="M29" t="n">
         <v>0.24</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.77</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1622</v>
+        <v>1572.25</v>
       </c>
       <c r="I30" t="n">
         <v>1575.941874366351</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.23</v>
+        <v>-5.23</v>
       </c>
       <c r="L30" t="n">
-        <v>3.84</v>
+        <v>5.65</v>
       </c>
       <c r="M30" t="n">
-        <v>0.77</v>
+        <v>1.97</v>
       </c>
       <c r="N30" t="n">
-        <v>1.05</v>
+        <v>3.55</v>
       </c>
       <c r="O30" t="n">
         <v>1.51</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>5.84</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45524.38541666666</v>
+        <v>45524.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>1591.15</v>
+        <v>1604</v>
       </c>
       <c r="I31" t="n">
         <v>1591.300912334439</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.2</v>
+        <v>-2.02</v>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>3.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.41</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1975.2</v>
+        <v>1903.95</v>
       </c>
       <c r="I32" t="n">
         <v>1915.612947085098</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>42</v>
+        <v>43.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>23.14</v>
+        <v>18.7</v>
       </c>
       <c r="L32" t="n">
         <v>1.03</v>
@@ -2265,7 +2648,7 @@
         <v>1.38</v>
       </c>
       <c r="N32" t="n">
-        <v>2.21</v>
+        <v>2.79</v>
       </c>
       <c r="O32" t="n">
         <v>3.42</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>7.08</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45631.38541666666</v>
+        <v>45631.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>1639.45</v>
+        <v>1647</v>
       </c>
       <c r="I33" t="n">
         <v>1640.130516953605</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>13.89</v>
+        <v>13.5</v>
       </c>
       <c r="L33" t="n">
         <v>3.47</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.21</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1627.9</v>
+        <v>1594.4</v>
       </c>
       <c r="I34" t="n">
         <v>1620.418517068713</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.16</v>
+        <v>-3.19</v>
       </c>
       <c r="L34" t="n">
-        <v>1.69</v>
+        <v>3.46</v>
       </c>
       <c r="M34" t="n">
-        <v>0.52</v>
+        <v>0.68</v>
       </c>
       <c r="N34" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="O34" t="n">
         <v>1.05</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>4.99</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>1577</v>
+        <v>1711.9</v>
       </c>
       <c r="I35" t="n">
         <v>1620.578484708873</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>1.09</v>
+        <v>-7.37</v>
       </c>
       <c r="L35" t="n">
-        <v>1.87</v>
+        <v>7.75</v>
       </c>
       <c r="M35" t="n">
         <v>0.83</v>
       </c>
       <c r="N35" t="n">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="O35" t="n">
         <v>-2.16</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1742.35</v>
+        <v>1693.4</v>
       </c>
       <c r="I36" t="n">
         <v>1713.073047137453</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K36" t="n">
-        <v>1.78</v>
+        <v>-1.08</v>
       </c>
       <c r="L36" t="n">
         <v>7.92</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>7.39</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45700.55208333334</v>
+        <v>45701.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1792.25</v>
+        <v>1835.3</v>
       </c>
       <c r="I37" t="n">
         <v>1818.468743773117</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.84</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>7.86</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="M37" t="n">
         <v>0.9</v>
       </c>
       <c r="N37" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
         <v>1.37</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>7.06</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45719.55208333334</v>
+        <v>45720.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1840</v>
+        <v>1792.6</v>
       </c>
       <c r="I38" t="n">
         <v>1839.15882772095</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>0.26</v>
+        <v>-2.33</v>
       </c>
       <c r="L38" t="n">
-        <v>2.11</v>
+        <v>2.58</v>
       </c>
       <c r="M38" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="O38" t="n">
         <v>2.8</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>6.71</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45733.38541666666</v>
+        <v>45733.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>1869.05</v>
+        <v>1875.1</v>
       </c>
       <c r="I39" t="n">
         <v>1870.710765388436</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.26</v>
+        <v>-4.6</v>
       </c>
       <c r="L39" t="n">
         <v>5.36</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.14</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1911.85</v>
+        <v>1832.05</v>
       </c>
       <c r="I40" t="n">
         <v>1908.751064731928</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>1.96</v>
+        <v>-2.3</v>
       </c>
       <c r="L40" t="n">
         <v>3.25</v>
       </c>
       <c r="M40" t="n">
-        <v>1.39</v>
+        <v>4.02</v>
       </c>
       <c r="N40" t="n">
-        <v>3.05</v>
+        <v>3.22</v>
       </c>
       <c r="O40" t="n">
         <v>3.77</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>7.66</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1900</v>
+        <v>1958</v>
       </c>
       <c r="I41" t="n">
         <v>1952.058382661336</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.71</v>
+        <v>-6.87</v>
       </c>
       <c r="L41" t="n">
-        <v>5.56</v>
+        <v>7.31</v>
       </c>
       <c r="M41" t="n">
         <v>2.14</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.2</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45776.55208333334</v>
+        <v>45777.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>2063.8</v>
+        <v>1944</v>
       </c>
       <c r="I42" t="n">
         <v>1996.044668659308</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>5.4</v>
+        <v>-0.72</v>
       </c>
       <c r="L42" t="n">
         <v>2.63</v>
       </c>
       <c r="M42" t="n">
-        <v>0.51</v>
+        <v>2.21</v>
       </c>
       <c r="N42" t="n">
-        <v>2.89</v>
+        <v>5.51</v>
       </c>
       <c r="O42" t="n">
         <v>2.44</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2012</v>
+        <v>2055.9</v>
       </c>
       <c r="I43" t="n">
         <v>2026.992201090179</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.5</v>
+        <v>-5.76</v>
       </c>
       <c r="L43" t="n">
         <v>6.53</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.12</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>2030</v>
+        <v>1960.4</v>
       </c>
       <c r="I44" t="n">
         <v>1988.463455711105</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>42.16666666666666</v>
+        <v>43</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.26</v>
+        <v>-4.65</v>
       </c>
       <c r="L44" t="n">
-        <v>5.12</v>
+        <v>5.98</v>
       </c>
       <c r="M44" t="n">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="N44" t="n">
         <v>2.36</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>4.9</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1920.6</v>
+        <v>2009.4</v>
       </c>
       <c r="I45" t="n">
         <v>1978.710306270775</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>2.03</v>
+        <v>-2.5</v>
       </c>
       <c r="L45" t="n">
         <v>3.19</v>
       </c>
       <c r="M45" t="n">
-        <v>0.47</v>
+        <v>1.53</v>
       </c>
       <c r="N45" t="n">
-        <v>0.79</v>
+        <v>3.87</v>
       </c>
       <c r="O45" t="n">
         <v>-2.2</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>5.77</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>2033</v>
+        <v>2004.5</v>
       </c>
       <c r="I46" t="n">
         <v>2028.08231516456</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K46" t="n">
-        <v>1.17</v>
+        <v>-0.24</v>
       </c>
       <c r="L46" t="n">
         <v>4.95</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>4.32</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45944.55208333334</v>
+        <v>45945.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>2019.9</v>
+        <v>2074</v>
       </c>
       <c r="I47" t="n">
         <v>2063.790296112867</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.77</v>
+        <v>-3.47</v>
       </c>
       <c r="L47" t="n">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="M47" t="n">
         <v>0.65</v>
       </c>
       <c r="N47" t="n">
-        <v>1.5</v>
+        <v>2.78</v>
       </c>
       <c r="O47" t="n">
         <v>-1.48</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.69</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45961.38541666666</v>
+        <v>45961.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>2103.7</v>
+        <v>2090</v>
       </c>
       <c r="I48" t="n">
         <v>2098.389113435996</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>1.43</v>
+        <v>0.77</v>
       </c>
       <c r="L48" t="n">
         <v>2.6</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>4.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1934</v>
+        <v>2013</v>
       </c>
       <c r="I49" t="n">
         <v>1987.971634372217</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>94</v>
+        <v>94.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>7.46</v>
+        <v>3.68</v>
       </c>
       <c r="L49" t="n">
         <v>1.76</v>
       </c>
       <c r="M49" t="n">
-        <v>0.97</v>
+        <v>4.43</v>
       </c>
       <c r="N49" t="n">
-        <v>2.52</v>
+        <v>3.98</v>
       </c>
       <c r="O49" t="n">
         <v>-1.32</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>127</v>
+        <v>128</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.44</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1994.6</v>
+        <v>1942.1</v>
       </c>
       <c r="I50" t="n">
         <v>1994.087019068088</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.91</v>
+        <v>-3.52</v>
       </c>
       <c r="L50" t="n">
-        <v>1.49</v>
+        <v>3.63</v>
       </c>
       <c r="M50" t="n">
-        <v>0.9</v>
+        <v>2.24</v>
       </c>
       <c r="N50" t="n">
-        <v>1.83</v>
+        <v>2.99</v>
       </c>
       <c r="O50" t="n">
         <v>3.98</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1684.1</v>
+        <v>1786.4</v>
       </c>
       <c r="I51" t="n">
         <v>1726.737042241425</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>36.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K51" t="n">
-        <v>13.28</v>
+        <v>8.02</v>
       </c>
       <c r="L51" t="n">
         <v>2.47</v>
       </c>
       <c r="M51" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>2.82</v>
+        <v>6.23</v>
       </c>
       <c r="O51" t="n">
         <v>-2.99</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>7.99</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1786.4</v>
+        <v>1760.1</v>
       </c>
       <c r="I52" t="n">
         <v>1767.209994959562</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>-1.47</v>
       </c>
       <c r="L52" t="n">
         <v>2.13</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>6.2</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46148.38541666666</v>
+        <v>46148.55208333334</v>
       </c>
       <c r="H53" t="n">
-        <v>1805.1</v>
+        <v>1836</v>
       </c>
       <c r="I53" t="n">
         <v>1834.670309048997</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.56</v>
+        <v>-4.31</v>
       </c>
       <c r="L53" t="n">
-        <v>4.06</v>
+        <v>4.47</v>
       </c>
       <c r="M53" t="n">
         <v>1.06</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>6.16</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46155.38541666666</v>
+        <v>46155.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>1744.2</v>
+        <v>1727</v>
       </c>
       <c r="I54" t="n">
         <v>1734.215116964823</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K54" t="n">
-        <v>-5</v>
+        <v>-5.94</v>
       </c>
       <c r="L54" t="n">
-        <v>5.66</v>
+        <v>5.99</v>
       </c>
       <c r="M54" t="n">
         <v>0.54</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.37</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46164.55208333334</v>
+        <v>46167.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1771</v>
+        <v>1803.4</v>
       </c>
       <c r="I55" t="n">
         <v>1799.191616384511</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.55</v>
+        <v>-4.42</v>
       </c>
       <c r="L55" t="n">
-        <v>3.32</v>
+        <v>4.63</v>
       </c>
       <c r="M55" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="N55" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="O55" t="n">
         <v>-1.2</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,25 +4283,25 @@
         <v>4.76</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46174.55208333334</v>
+        <v>46175.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1760.6</v>
+        <v>1741.9</v>
       </c>
       <c r="I56" t="n">
         <v>1746.530892510975</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K56" t="n">
-        <v>-2.37</v>
+        <v>-3.41</v>
       </c>
       <c r="L56" t="n">
-        <v>2.63</v>
+        <v>4.95</v>
       </c>
       <c r="M56" t="n">
-        <v>0.59</v>
+        <v>0.71</v>
       </c>
       <c r="N56" t="n">
         <v>2.07</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.79</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1691.9</v>
+        <v>1753.6</v>
       </c>
       <c r="I57" t="n">
         <v>1715.626042757772</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>2.87</v>
+        <v>-0.67</v>
       </c>
       <c r="L57" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="M57" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="N57" t="n">
-        <v>2.66</v>
+        <v>3.42</v>
       </c>
       <c r="O57" t="n">
         <v>-0.65</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>6</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46219.38541666666</v>
+        <v>46219.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>1838</v>
+        <v>1830</v>
       </c>
       <c r="I58" t="n">
         <v>1830.561050838453</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>4.81</v>
+        <v>4.36</v>
       </c>
       <c r="L58" t="n">
         <v>2.49</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.59</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46230.38541666666</v>
+        <v>46230.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>1912.9</v>
+        <v>1919.9</v>
       </c>
       <c r="I59" t="n">
         <v>1914.078513040403</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.53</v>
+        <v>-4.91</v>
       </c>
       <c r="L59" t="n">
-        <v>4.58</v>
+        <v>4.92</v>
       </c>
       <c r="M59" t="n">
         <v>0.33</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.32</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>2084.5</v>
+        <v>1993.1</v>
       </c>
       <c r="I60" t="n">
         <v>2004.961718735544</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K60" t="n">
-        <v>8.57</v>
+        <v>3.81</v>
       </c>
       <c r="L60" t="n">
         <v>1.44</v>
       </c>
       <c r="M60" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="N60" t="n">
-        <v>0.93</v>
+        <v>3.86</v>
       </c>
       <c r="O60" t="n">
         <v>2.12</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3921,6 +4652,14 @@
       <c r="Q61" t="n">
         <v>112</v>
       </c>
+      <c r="R61" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6023,7 +6762,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.3</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="6">
@@ -6033,7 +6772,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -6043,7 +6782,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.2</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -6053,7 +6792,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -6063,7 +6802,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="10">
@@ -6073,7 +6812,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48.3</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="11">
@@ -6083,7 +6822,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -6093,7 +6832,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6103,7 +6842,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64.40000000000001</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="14">
@@ -6113,7 +6852,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.98</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="15">
@@ -6123,7 +6862,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.44</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="16">
@@ -6133,7 +6872,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.51</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="17">
@@ -6143,7 +6882,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>36.88</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="18">
@@ -6153,7 +6892,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54.2</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="19">
@@ -6163,7 +6902,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.35</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="20">
@@ -6173,7 +6912,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.96</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="21">
@@ -6183,7 +6922,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.380000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -6193,7 +6932,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -6213,7 +6952,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="25">
@@ -6223,7 +6962,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.3</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="26">
@@ -6233,7 +6972,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="27">
@@ -6243,7 +6982,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.98</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="28">
@@ -6253,7 +6992,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
